--- a/dev/CodeSystem-PHFDACPRCS.xlsx
+++ b/dev/CodeSystem-PHFDACPRCS.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://verification.fda.gov.ph/</t>
+    <t>https://verification.fda.gov.ph</t>
   </si>
   <si>
     <t>Version</t>
@@ -79,7 +79,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Philippines</t>
+    <t>Philippines (the)</t>
   </si>
   <si>
     <t>Description</t>

--- a/dev/CodeSystem-PHFDACPRCS.xlsx
+++ b/dev/CodeSystem-PHFDACPRCS.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
